--- a/artfynd/A 61174-2025 artfynd.xlsx
+++ b/artfynd/A 61174-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53949928</v>
+        <v>357275</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,28 +703,17 @@
           <t>W. C. R. Watson</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röe, 250 m SV om Kolvik, granskog, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>290918.7552792187</v>
+        <v>290919</v>
       </c>
       <c r="R2" t="n">
-        <v>6479940.484044866</v>
+        <v>6479940</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,32 +740,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>OB-Lys-0333</t>
+          <t>Arkiv-OB-Lys-0189</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Klena buskar under höga granar</t>
+          <t>finns</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,20 +767,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Falk</t>
+          <t>Bohuslän Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Falk</t>
+          <t>Bohuslän Floraväktarna, Eva Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 61174-2025 artfynd.xlsx
+++ b/artfynd/A 61174-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,8 +793,16 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/357275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>